--- a/WorkBot/main/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Collegetown_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Collegetown_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,85 +524,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40834</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Trash Bag (38x58)</t>
+          <t>Cup - Cold (24oz)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>45.73</v>
+        <v>70.67</v>
       </c>
       <c r="E8" t="n">
-        <v>45.73</v>
+        <v>141.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cup - Cold (24oz)</t>
+          <t>Cup - Cold (16oz)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>70.67</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>141.34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>40280</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cup - Cold (16oz)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>84.43000000000001</v>
-      </c>
-      <c r="E10" t="n">
         <v>168.86</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>27029</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bag Paper - Handle (Small)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>37.3</v>
       </c>
     </row>
   </sheetData>
